--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="638">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,1381 +44,1384 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダークマター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest,wooden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森から生まれし,木の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄塊と呼ばれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラナイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rigid,stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩をも砕く,石の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">練習用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深い草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子供のおもちゃの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゼリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trembling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プルプルする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生もの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカシア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄金に輝く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreadbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を砕く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雷を帯し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気高き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミカ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ephemeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">儚き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unveiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真実を暴く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイヤモンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">everlasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変わることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubynus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルビナス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤く染まった</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由緒ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珊瑚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quartz sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珪砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glittering,glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さざめく,ガラスの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminescent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異光を放つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">革</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全てを包む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draconic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜を統べし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真珠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を照らす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エメラルド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇跡を呼ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コバルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adamantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アダマンタイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthshaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大地を揺るがす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapphire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サファイア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トパーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquamarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アクアマリン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オパール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翡翠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニキス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapis lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラピス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターコイズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meteorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メテオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platinum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brilliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不死なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふざけた</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エーテル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永遠なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライムストーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大理石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バサルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒曜石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">godbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神殺しの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phyllite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot spring water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pale soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い色の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mahogany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マホガニー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rosewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farmwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">農作業用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミスリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ancient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイタニアム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色褪せぬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">綿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beautiful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美しき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逆鱗に触れし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cashmere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カシミア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暖かなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザイロン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異国からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spirit cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">霊布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherworldly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この世ならざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawn cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵晒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵闇をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">griffon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼鳥鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼を折られし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プラスチック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透き通った</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柔らかい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spider silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜘蛛糸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entangled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絡みつく</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モミ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パルル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明るい土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tropical water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南の島の水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強靭なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cherryblossom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">桜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加工物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poplar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポプラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amethyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アメジスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bewitching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖艶なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フェイウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coralwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーラルウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズクオーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛らしい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh cream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生クリーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">琥珀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マグマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真なる黒曜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lawbreaking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">摂理を断つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elder gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エルダーゴールド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄昏の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orichalcum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オリハルコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unbreakable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砕けることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abyssal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵を映す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netherite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネザライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infernal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉獄で鍛えられし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
-    <t xml:space="preserve">dark matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダークマター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distortive </t>
-  </si>
-  <si>
-    <t xml:space="preserve">存在を歪ませる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オーク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest,wooden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森から生まれし,木の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄塊と呼ばれる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラナイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rigid,stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩をも砕く,石の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">練習用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深い草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子供のおもちゃの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゼリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trembling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プルプルする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生もの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アカシア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄金に輝く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dreadbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を砕く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雷を帯し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">気高き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミカ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ephemeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">儚き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chromite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真実を暴く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイヤモンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ever lasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろいなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubynus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルビナス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤く染まった</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">historic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">由緒ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珊瑚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quartz sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珪砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glittering,glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">さざめく,ガラスの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異光を放つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">革</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mysterious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全てを包む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragonbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜を統べし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真珠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を照らす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エメラルド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇跡を呼ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cobalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コバルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adamantite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アダマンタイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">earthshaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大地を揺るがす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapphire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サファイア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トパーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquamarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アクアマリン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オパール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翡翠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onyx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オニキス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapis lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラピス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターコイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meteorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メテオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platinum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brilliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不死なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">birch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふざけた</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エーテル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永遠なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ライムストーン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大理石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バサルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黒曜石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">godbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神殺しの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phyllite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot spring water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pale soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い色の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahogany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マホガニー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rosewood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farmwork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">農作業用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cedar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mithril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミスリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titanium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイタニアム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">色褪せぬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">綿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightweight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beautiful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">美しき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逆鱗に触れし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashmere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カシミア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暖かなる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zylon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ザイロン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異国からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spirit cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">霊布</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otherworldly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この世ならざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dawn cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵晒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dusk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵闇をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">griffon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼鳥鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼を折られし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラスチック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transparent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">透き通った</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柔らかい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蜘蛛糸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entangled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絡みつく</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モミ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パルル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明るい土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tropical water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南の島の水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">white sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">強靭なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">willow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cherryblossom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">桜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加工物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">炭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poplar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポプラ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bamboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amethyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメジスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bewitching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖艶なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フェイウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coralwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーラルウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rose quartz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズクオーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lovely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛らしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh cream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生クリーム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">琥珀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マグマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真なる黒曜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">antinomic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">摂理を断つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elder gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エルダーゴールド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shimmering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">緋色に煌めく </t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orichalcum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オリハルコン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unbreakable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砕けることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abyssal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵を映す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">netherite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネザライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">purgatorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">煉獄で鍛えられし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無限の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
+    <t xml:space="preserve">EA 23.108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 15.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta 22.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.92 Patch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.229 Patch 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.237 Patch 1</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 15.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beta 22.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.92 Patch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.229 Patch 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
   </si>
   <si>
     <t xml:space="preserve">다크 매터</t>
@@ -2031,10 +2034,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>458</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2043,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -2060,7 +2063,7 @@
         <v>459</v>
       </c>
       <c r="C4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -2069,7 +2072,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2086,7 +2089,7 @@
         <v>458</v>
       </c>
       <c r="C5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -2095,7 +2098,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -2112,7 +2115,7 @@
         <v>458</v>
       </c>
       <c r="C6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -2121,7 +2124,7 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -2135,10 +2138,10 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -2147,7 +2150,7 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -2160,7 +2163,7 @@
         <v>458</v>
       </c>
       <c r="C8" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -2169,7 +2172,7 @@
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G8" t="s">
         <v>35</v>
@@ -2183,10 +2186,10 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
@@ -2195,7 +2198,7 @@
         <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -2205,10 +2208,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
@@ -2217,7 +2220,7 @@
         <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
@@ -2230,7 +2233,7 @@
         <v>458</v>
       </c>
       <c r="C11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -2239,7 +2242,7 @@
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G11" t="s">
         <v>46</v>
@@ -2256,7 +2259,7 @@
         <v>458</v>
       </c>
       <c r="C12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2265,7 +2268,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G12" t="s">
         <v>51</v>
@@ -2282,7 +2285,7 @@
         <v>458</v>
       </c>
       <c r="C13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2291,7 +2294,7 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G13" t="s">
         <v>56</v>
@@ -2305,10 +2308,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -2317,7 +2320,7 @@
         <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
@@ -2330,7 +2333,7 @@
         <v>458</v>
       </c>
       <c r="C15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -2339,7 +2342,7 @@
         <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G15" t="s">
         <v>64</v>
@@ -2356,7 +2359,7 @@
         <v>458</v>
       </c>
       <c r="C16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D16" t="s">
         <v>67</v>
@@ -2365,7 +2368,7 @@
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G16" t="s">
         <v>69</v>
@@ -2382,7 +2385,7 @@
         <v>458</v>
       </c>
       <c r="C17" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -2391,7 +2394,7 @@
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -2408,7 +2411,7 @@
         <v>458</v>
       </c>
       <c r="C18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -2417,7 +2420,7 @@
         <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G18" t="s">
         <v>79</v>
@@ -2434,7 +2437,7 @@
         <v>458</v>
       </c>
       <c r="C19" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -2443,7 +2446,7 @@
         <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G19" t="s">
         <v>84</v>
@@ -2460,7 +2463,7 @@
         <v>458</v>
       </c>
       <c r="C20" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D20" t="s">
         <v>87</v>
@@ -2469,7 +2472,7 @@
         <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G20" t="s">
         <v>89</v>
@@ -2483,10 +2486,10 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>461</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D21" t="s">
         <v>92</v>
@@ -2495,7 +2498,7 @@
         <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>94</v>
@@ -2512,7 +2515,7 @@
         <v>462</v>
       </c>
       <c r="C22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -2521,7 +2524,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -2538,7 +2541,7 @@
         <v>458</v>
       </c>
       <c r="C23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D23" t="s">
         <v>102</v>
@@ -2547,7 +2550,7 @@
         <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G23" t="s">
         <v>104</v>
@@ -2564,7 +2567,7 @@
         <v>458</v>
       </c>
       <c r="C24" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D24" t="s">
         <v>107</v>
@@ -2573,7 +2576,7 @@
         <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G24" t="s">
         <v>109</v>
@@ -2590,7 +2593,7 @@
         <v>459</v>
       </c>
       <c r="C25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
@@ -2599,7 +2602,7 @@
         <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G25" t="s">
         <v>114</v>
@@ -2616,7 +2619,7 @@
         <v>458</v>
       </c>
       <c r="C26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D26" t="s">
         <v>117</v>
@@ -2625,7 +2628,7 @@
         <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G26" t="s">
         <v>119</v>
@@ -2642,7 +2645,7 @@
         <v>458</v>
       </c>
       <c r="C27" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D27" t="s">
         <v>122</v>
@@ -2651,7 +2654,7 @@
         <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G27" t="s">
         <v>124</v>
@@ -2668,7 +2671,7 @@
         <v>458</v>
       </c>
       <c r="C28" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D28" t="s">
         <v>127</v>
@@ -2677,7 +2680,7 @@
         <v>128</v>
       </c>
       <c r="F28" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G28" t="s">
         <v>129</v>
@@ -2694,7 +2697,7 @@
         <v>458</v>
       </c>
       <c r="C29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D29" t="s">
         <v>132</v>
@@ -2703,7 +2706,7 @@
         <v>133</v>
       </c>
       <c r="F29" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G29" t="s">
         <v>134</v>
@@ -2720,7 +2723,7 @@
         <v>458</v>
       </c>
       <c r="C30" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
@@ -2729,7 +2732,7 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G30" t="s">
         <v>139</v>
@@ -2743,10 +2746,10 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -2755,7 +2758,7 @@
         <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
@@ -2768,7 +2771,7 @@
         <v>458</v>
       </c>
       <c r="C32" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -2777,7 +2780,7 @@
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="G32" t="s">
         <v>147</v>
@@ -2791,10 +2794,10 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C33" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D33" t="s">
         <v>150</v>
@@ -2803,7 +2806,7 @@
         <v>151</v>
       </c>
       <c r="F33" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -2813,10 +2816,10 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C34" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -2825,7 +2828,7 @@
         <v>154</v>
       </c>
       <c r="F34" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
@@ -2835,10 +2838,10 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C35" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -2847,7 +2850,7 @@
         <v>157</v>
       </c>
       <c r="F35" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
@@ -2857,10 +2860,10 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C36" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
@@ -2869,7 +2872,7 @@
         <v>160</v>
       </c>
       <c r="F36" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
@@ -2879,10 +2882,10 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C37" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -2891,7 +2894,7 @@
         <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
@@ -2901,10 +2904,10 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C38" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D38" t="s">
         <v>165</v>
@@ -2913,7 +2916,7 @@
         <v>166</v>
       </c>
       <c r="F38" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
@@ -2923,10 +2926,10 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C39" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D39" t="s">
         <v>168</v>
@@ -2935,7 +2938,7 @@
         <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
@@ -2945,10 +2948,10 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C40" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D40" t="s">
         <v>171</v>
@@ -2957,7 +2960,7 @@
         <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -2967,10 +2970,10 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C41" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D41" t="s">
         <v>174</v>
@@ -2979,7 +2982,7 @@
         <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
@@ -2992,7 +2995,7 @@
         <v>458</v>
       </c>
       <c r="C42" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -3001,7 +3004,7 @@
         <v>178</v>
       </c>
       <c r="F42" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G42" t="s">
         <v>179</v>
@@ -3018,7 +3021,7 @@
         <v>458</v>
       </c>
       <c r="C43" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -3027,7 +3030,7 @@
         <v>183</v>
       </c>
       <c r="F43" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G43" t="s">
         <v>184</v>
@@ -3041,10 +3044,10 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C44" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D44" t="s">
         <v>187</v>
@@ -3053,7 +3056,7 @@
         <v>188</v>
       </c>
       <c r="F44" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
@@ -3066,7 +3069,7 @@
         <v>458</v>
       </c>
       <c r="C45" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D45" t="s">
         <v>190</v>
@@ -3075,7 +3078,7 @@
         <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G45" t="s">
         <v>192</v>
@@ -3092,7 +3095,7 @@
         <v>458</v>
       </c>
       <c r="C46" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D46" t="s">
         <v>195</v>
@@ -3101,7 +3104,7 @@
         <v>196</v>
       </c>
       <c r="F46" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G46" t="s">
         <v>197</v>
@@ -3115,10 +3118,10 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C47" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D47" t="s">
         <v>200</v>
@@ -3127,7 +3130,7 @@
         <v>201</v>
       </c>
       <c r="F47" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
@@ -3137,10 +3140,10 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C48" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D48" t="s">
         <v>203</v>
@@ -3149,7 +3152,7 @@
         <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -3159,10 +3162,10 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C49" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D49" t="s">
         <v>206</v>
@@ -3171,7 +3174,7 @@
         <v>207</v>
       </c>
       <c r="F49" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
@@ -3181,10 +3184,10 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C50" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D50" t="s">
         <v>209</v>
@@ -3193,7 +3196,7 @@
         <v>210</v>
       </c>
       <c r="F50" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
@@ -3203,10 +3206,10 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C51" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D51" t="s">
         <v>212</v>
@@ -3215,7 +3218,7 @@
         <v>213</v>
       </c>
       <c r="F51" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -3225,10 +3228,10 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C52" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D52" t="s">
         <v>215</v>
@@ -3237,7 +3240,7 @@
         <v>216</v>
       </c>
       <c r="F52" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -3247,10 +3250,10 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C53" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D53" t="s">
         <v>218</v>
@@ -3259,7 +3262,7 @@
         <v>219</v>
       </c>
       <c r="F53" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -3269,10 +3272,10 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C54" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D54" t="s">
         <v>221</v>
@@ -3281,7 +3284,7 @@
         <v>222</v>
       </c>
       <c r="F54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -3291,10 +3294,10 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C55" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D55" t="s">
         <v>224</v>
@@ -3303,7 +3306,7 @@
         <v>225</v>
       </c>
       <c r="F55" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -3313,10 +3316,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C56" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3325,7 +3328,7 @@
         <v>228</v>
       </c>
       <c r="F56" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -3335,10 +3338,10 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C57" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3347,7 +3350,7 @@
         <v>231</v>
       </c>
       <c r="F57" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -3360,7 +3363,7 @@
         <v>459</v>
       </c>
       <c r="C58" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3369,7 +3372,7 @@
         <v>234</v>
       </c>
       <c r="F58" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
@@ -3383,10 +3386,10 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C59" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D59" t="s">
         <v>238</v>
@@ -3395,7 +3398,7 @@
         <v>239</v>
       </c>
       <c r="F59" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -3405,10 +3408,10 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C60" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
@@ -3417,7 +3420,7 @@
         <v>242</v>
       </c>
       <c r="F60" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -3427,10 +3430,10 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C61" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
@@ -3439,7 +3442,7 @@
         <v>245</v>
       </c>
       <c r="F61" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -3449,10 +3452,10 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C62" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D62" t="s">
         <v>247</v>
@@ -3461,7 +3464,7 @@
         <v>248</v>
       </c>
       <c r="F62" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -3471,10 +3474,10 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C63" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D63" t="s">
         <v>250</v>
@@ -3483,7 +3486,7 @@
         <v>251</v>
       </c>
       <c r="F63" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -3493,10 +3496,10 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C64" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D64" t="s">
         <v>253</v>
@@ -3505,7 +3508,7 @@
         <v>254</v>
       </c>
       <c r="F64" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -3518,7 +3521,7 @@
         <v>458</v>
       </c>
       <c r="C65" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D65" t="s">
         <v>256</v>
@@ -3527,7 +3530,7 @@
         <v>257</v>
       </c>
       <c r="F65" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G65" t="s">
         <v>258</v>
@@ -3541,10 +3544,10 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C66" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D66" t="s">
         <v>261</v>
@@ -3553,7 +3556,7 @@
         <v>262</v>
       </c>
       <c r="F66" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -3563,10 +3566,10 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C67" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D67" t="s">
         <v>264</v>
@@ -3575,7 +3578,7 @@
         <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -3585,10 +3588,10 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C68" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D68" t="s">
         <v>267</v>
@@ -3597,7 +3600,7 @@
         <v>268</v>
       </c>
       <c r="F68" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -3607,10 +3610,10 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C69" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D69" t="s">
         <v>270</v>
@@ -3619,7 +3622,7 @@
         <v>271</v>
       </c>
       <c r="F69" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -3629,10 +3632,10 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C70" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D70" t="s">
         <v>273</v>
@@ -3641,7 +3644,7 @@
         <v>274</v>
       </c>
       <c r="F70" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -3654,7 +3657,7 @@
         <v>458</v>
       </c>
       <c r="C71" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D71" t="s">
         <v>276</v>
@@ -3663,7 +3666,7 @@
         <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G71" t="s">
         <v>278</v>
@@ -3680,7 +3683,7 @@
         <v>458</v>
       </c>
       <c r="C72" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D72" t="s">
         <v>281</v>
@@ -3689,7 +3692,7 @@
         <v>282</v>
       </c>
       <c r="F72" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G72" t="s">
         <v>283</v>
@@ -3706,7 +3709,7 @@
         <v>459</v>
       </c>
       <c r="C73" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D73" t="s">
         <v>286</v>
@@ -3715,7 +3718,7 @@
         <v>287</v>
       </c>
       <c r="F73" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G73" t="s">
         <v>288</v>
@@ -3732,7 +3735,7 @@
         <v>458</v>
       </c>
       <c r="C74" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D74" t="s">
         <v>291</v>
@@ -3741,7 +3744,7 @@
         <v>292</v>
       </c>
       <c r="F74" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G74" t="s">
         <v>293</v>
@@ -3758,7 +3761,7 @@
         <v>458</v>
       </c>
       <c r="C75" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D75" t="s">
         <v>296</v>
@@ -3767,7 +3770,7 @@
         <v>297</v>
       </c>
       <c r="F75" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G75" t="s">
         <v>298</v>
@@ -3784,7 +3787,7 @@
         <v>459</v>
       </c>
       <c r="C76" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D76" t="s">
         <v>301</v>
@@ -3793,7 +3796,7 @@
         <v>302</v>
       </c>
       <c r="F76" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G76" t="s">
         <v>303</v>
@@ -3810,7 +3813,7 @@
         <v>458</v>
       </c>
       <c r="C77" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D77" t="s">
         <v>306</v>
@@ -3819,7 +3822,7 @@
         <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G77" t="s">
         <v>308</v>
@@ -3836,7 +3839,7 @@
         <v>458</v>
       </c>
       <c r="C78" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D78" t="s">
         <v>311</v>
@@ -3845,7 +3848,7 @@
         <v>312</v>
       </c>
       <c r="F78" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G78" t="s">
         <v>313</v>
@@ -3862,7 +3865,7 @@
         <v>458</v>
       </c>
       <c r="C79" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D79" t="s">
         <v>316</v>
@@ -3871,7 +3874,7 @@
         <v>317</v>
       </c>
       <c r="F79" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G79" t="s">
         <v>318</v>
@@ -3888,7 +3891,7 @@
         <v>458</v>
       </c>
       <c r="C80" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D80" t="s">
         <v>321</v>
@@ -3897,7 +3900,7 @@
         <v>322</v>
       </c>
       <c r="F80" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G80" t="s">
         <v>323</v>
@@ -3914,7 +3917,7 @@
         <v>458</v>
       </c>
       <c r="C81" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D81" t="s">
         <v>326</v>
@@ -3923,7 +3926,7 @@
         <v>327</v>
       </c>
       <c r="F81" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G81" t="s">
         <v>328</v>
@@ -3937,10 +3940,10 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C82" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D82" t="s">
         <v>331</v>
@@ -3949,7 +3952,7 @@
         <v>332</v>
       </c>
       <c r="F82" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
@@ -3962,7 +3965,7 @@
         <v>459</v>
       </c>
       <c r="C83" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D83" t="s">
         <v>334</v>
@@ -3971,7 +3974,7 @@
         <v>335</v>
       </c>
       <c r="F83" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G83" t="s">
         <v>336</v>
@@ -3988,7 +3991,7 @@
         <v>459</v>
       </c>
       <c r="C84" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D84" t="s">
         <v>339</v>
@@ -3997,7 +4000,7 @@
         <v>340</v>
       </c>
       <c r="F84" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G84" t="s">
         <v>341</v>
@@ -4011,10 +4014,10 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C85" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D85" t="s">
         <v>344</v>
@@ -4023,7 +4026,7 @@
         <v>345</v>
       </c>
       <c r="F85" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
@@ -4033,10 +4036,10 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C86" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D86" t="s">
         <v>347</v>
@@ -4045,7 +4048,7 @@
         <v>348</v>
       </c>
       <c r="F86" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
@@ -4055,10 +4058,10 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C87" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D87" t="s">
         <v>350</v>
@@ -4067,7 +4070,7 @@
         <v>351</v>
       </c>
       <c r="F87" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
@@ -4077,10 +4080,10 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C88" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D88" t="s">
         <v>353</v>
@@ -4089,7 +4092,7 @@
         <v>354</v>
       </c>
       <c r="F88" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
@@ -4099,10 +4102,10 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C89" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D89" t="s">
         <v>356</v>
@@ -4111,7 +4114,7 @@
         <v>357</v>
       </c>
       <c r="F89" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
@@ -4121,10 +4124,10 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C90" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D90" t="s">
         <v>359</v>
@@ -4133,7 +4136,7 @@
         <v>360</v>
       </c>
       <c r="F90" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
@@ -4143,10 +4146,10 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C91" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D91" t="s">
         <v>362</v>
@@ -4155,7 +4158,7 @@
         <v>363</v>
       </c>
       <c r="F91" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
@@ -4165,10 +4168,10 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C92" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D92" t="s">
         <v>365</v>
@@ -4177,7 +4180,7 @@
         <v>366</v>
       </c>
       <c r="F92" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
@@ -4187,10 +4190,10 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C93" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D93" t="s">
         <v>368</v>
@@ -4199,7 +4202,7 @@
         <v>369</v>
       </c>
       <c r="F93" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
@@ -4212,7 +4215,7 @@
         <v>459</v>
       </c>
       <c r="C94" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D94" t="s">
         <v>371</v>
@@ -4221,7 +4224,7 @@
         <v>372</v>
       </c>
       <c r="F94" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G94" t="s">
         <v>373</v>
@@ -4235,10 +4238,10 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C95" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D95" t="s">
         <v>376</v>
@@ -4247,7 +4250,7 @@
         <v>377</v>
       </c>
       <c r="F95" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
@@ -4257,10 +4260,10 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C96" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D96" t="s">
         <v>379</v>
@@ -4269,7 +4272,7 @@
         <v>380</v>
       </c>
       <c r="F96" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
@@ -4279,10 +4282,10 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C97" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D97" t="s">
         <v>382</v>
@@ -4291,7 +4294,7 @@
         <v>383</v>
       </c>
       <c r="F97" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
@@ -4301,10 +4304,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C98" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D98" t="s">
         <v>385</v>
@@ -4313,7 +4316,7 @@
         <v>386</v>
       </c>
       <c r="F98" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -4323,10 +4326,10 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C99" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D99" t="s">
         <v>388</v>
@@ -4335,7 +4338,7 @@
         <v>389</v>
       </c>
       <c r="F99" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
@@ -4345,10 +4348,10 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C100" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D100" t="s">
         <v>391</v>
@@ -4357,7 +4360,7 @@
         <v>392</v>
       </c>
       <c r="F100" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
@@ -4367,10 +4370,10 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>460</v>
       </c>
       <c r="C101" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D101" t="s">
         <v>394</v>
@@ -4379,7 +4382,7 @@
         <v>395</v>
       </c>
       <c r="F101" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
@@ -4392,7 +4395,7 @@
         <v>463</v>
       </c>
       <c r="C102" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D102" t="s">
         <v>397</v>
@@ -4401,7 +4404,7 @@
         <v>398</v>
       </c>
       <c r="F102" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G102" t="s">
         <v>399</v>
@@ -4418,7 +4421,7 @@
         <v>464</v>
       </c>
       <c r="C103" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D103" t="s">
         <v>402</v>
@@ -4437,7 +4440,7 @@
         <v>464</v>
       </c>
       <c r="C104" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D104" t="s">
         <v>405</v>
@@ -4456,7 +4459,7 @@
         <v>461</v>
       </c>
       <c r="C105" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D105" t="s">
         <v>408</v>
@@ -4465,7 +4468,7 @@
         <v>409</v>
       </c>
       <c r="F105" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G105" t="s">
         <v>410</v>
@@ -4482,7 +4485,7 @@
         <v>465</v>
       </c>
       <c r="C106" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D106" t="s">
         <v>413</v>
@@ -4501,7 +4504,7 @@
         <v>466</v>
       </c>
       <c r="C107" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D107" t="s">
         <v>416</v>
@@ -4520,7 +4523,7 @@
         <v>467</v>
       </c>
       <c r="C108" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D108" t="s">
         <v>419</v>
@@ -4539,7 +4542,7 @@
         <v>467</v>
       </c>
       <c r="C109" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D109" t="s">
         <v>422</v>
@@ -4555,10 +4558,10 @@
         <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C110" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D110" t="s">
         <v>425</v>
@@ -4567,7 +4570,7 @@
         <v>426</v>
       </c>
       <c r="F110" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G110" t="s">
         <v>427</v>
@@ -4581,10 +4584,10 @@
         <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>460</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D111" t="s">
         <v>430</v>
@@ -4593,140 +4596,140 @@
         <v>431</v>
       </c>
       <c r="F111" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G111" t="s">
+        <v>318</v>
+      </c>
+      <c r="H111" t="s">
         <v>432</v>
-      </c>
-      <c r="H111" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>433</v>
+      </c>
+      <c r="B112" t="s">
+        <v>468</v>
+      </c>
+      <c r="C112" t="s">
+        <v>578</v>
+      </c>
+      <c r="D112" t="s">
         <v>434</v>
       </c>
-      <c r="B112" t="s">
-        <v>460</v>
-      </c>
-      <c r="C112" t="s">
-        <v>577</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>435</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>633</v>
+      </c>
+      <c r="G112" t="s">
         <v>436</v>
       </c>
-      <c r="F112" t="s">
-        <v>632</v>
-      </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>437</v>
-      </c>
-      <c r="H112" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
+        <v>438</v>
+      </c>
+      <c r="B113" t="s">
+        <v>468</v>
+      </c>
+      <c r="C113" t="s">
+        <v>579</v>
+      </c>
+      <c r="D113" t="s">
         <v>439</v>
       </c>
-      <c r="B113" t="s">
-        <v>460</v>
-      </c>
-      <c r="C113" t="s">
-        <v>578</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>440</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
+        <v>634</v>
+      </c>
+      <c r="G113" t="s">
         <v>441</v>
       </c>
-      <c r="F113" t="s">
-        <v>633</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>442</v>
-      </c>
-      <c r="H113" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>443</v>
+      </c>
+      <c r="B114" t="s">
+        <v>468</v>
+      </c>
+      <c r="C114" t="s">
+        <v>580</v>
+      </c>
+      <c r="D114" t="s">
         <v>444</v>
       </c>
-      <c r="B114" t="s">
-        <v>460</v>
-      </c>
-      <c r="C114" t="s">
-        <v>579</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>445</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>635</v>
+      </c>
+      <c r="G114" t="s">
         <v>446</v>
       </c>
-      <c r="F114" t="s">
-        <v>634</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>447</v>
-      </c>
-      <c r="H114" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>448</v>
+      </c>
+      <c r="B115" t="s">
+        <v>468</v>
+      </c>
+      <c r="C115" t="s">
+        <v>581</v>
+      </c>
+      <c r="D115" t="s">
         <v>449</v>
       </c>
-      <c r="B115" t="s">
-        <v>460</v>
-      </c>
-      <c r="C115" t="s">
-        <v>580</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>450</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
+        <v>636</v>
+      </c>
+      <c r="G115" t="s">
         <v>451</v>
       </c>
-      <c r="F115" t="s">
-        <v>635</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>452</v>
-      </c>
-      <c r="H115" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
+        <v>453</v>
+      </c>
+      <c r="B116" t="s">
+        <v>468</v>
+      </c>
+      <c r="C116" t="s">
+        <v>582</v>
+      </c>
+      <c r="D116" t="s">
         <v>454</v>
       </c>
-      <c r="B116" t="s">
-        <v>460</v>
-      </c>
-      <c r="C116" t="s">
-        <v>581</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>455</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
+        <v>637</v>
+      </c>
+      <c r="G116" t="s">
         <v>456</v>
-      </c>
-      <c r="F116" t="s">
-        <v>636</v>
-      </c>
-      <c r="G116" t="s">
-        <v>283</v>
       </c>
       <c r="H116" t="s">
         <v>457</v>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="639">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,1363 +44,1363 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダークマター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest,wooden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森から生まれし,木の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄塊と呼ばれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラナイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rigid,stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩をも砕く,石の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">練習用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深い草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子供のおもちゃの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゼリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trembling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プルプルする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生もの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカシア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄金に輝く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreadbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を砕く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雷を帯し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気高き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミカ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ephemeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">儚き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unveiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真実を暴く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイヤモンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">everlasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変わることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubynus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルビナス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤く染まった</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由緒ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珊瑚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quartz sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珪砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glittering,glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さざめく,ガラスの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminescent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異光を放つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">革</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全てを包む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draconic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜を統べし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真珠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を照らす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エメラルド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇跡を呼ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コバルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adamantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アダマンタイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthshaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大地を揺るがす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapphire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サファイア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トパーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquamarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アクアマリン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オパール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翡翠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニキス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapis lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラピス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターコイズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meteorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メテオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platinum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brilliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不死なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふざけた</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エーテル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永遠なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライムストーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大理石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バサルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒曜石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">godbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神殺しの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phyllite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot spring water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pale soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い色の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mahogany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マホガニー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rosewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farmwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">農作業用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミスリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ancient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイタニアム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色褪せぬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">綿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beautiful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美しき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逆鱗に触れし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cashmere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カシミア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暖かなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザイロン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異国からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spirit cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">霊布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherworldly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この世ならざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawn cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵晒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵闇をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">griffon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼鳥鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼を折られし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プラスチック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透き通った</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柔らかい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spider silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜘蛛糸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entangled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絡みつく</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モミ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パルル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明るい土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tropical water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南の島の水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強靭なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cherryblossom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">桜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加工物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poplar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポプラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amethyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アメジスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bewitching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖艶なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フェイウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coralwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーラルウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズクオーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛らしい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh cream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生クリーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">琥珀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マグマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真なる黒曜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lawbreaking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">摂理を断つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elder gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エルダーゴールド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄昏の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orichalcum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オリハルコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unbreakable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砕けることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abyssal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵を映す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netherite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネザライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infernal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉獄で鍛えられし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dark matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダークマター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オーク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest,wooden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森から生まれし,木の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄塊と呼ばれる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラナイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rigid,stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩をも砕く,石の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">練習用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深い草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子供のおもちゃの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゼリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trembling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プルプルする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生もの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アカシア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄金に輝く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dreadbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を砕く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雷を帯し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">気高き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミカ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ephemeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">儚き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chromite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unveiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真実を暴く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイヤモンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everlasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変わることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubynus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルビナス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤く染まった</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">historic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">由緒ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珊瑚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quartz sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珪砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glittering,glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">さざめく,ガラスの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異光を放つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">革</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mysterious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全てを包む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draconic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜を統べし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真珠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を照らす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エメラルド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇跡を呼ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cobalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コバルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adamantite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アダマンタイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">earthshaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大地を揺るがす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapphire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サファイア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トパーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquamarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アクアマリン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オパール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翡翠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onyx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オニキス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapis lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラピス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターコイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meteorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メテオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platinum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brilliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不死なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">birch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふざけた</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エーテル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永遠なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ライムストーン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大理石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バサルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黒曜石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">godbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神殺しの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phyllite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot spring water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pale soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い色の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahogany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マホガニー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rosewood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farmwork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">農作業用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cedar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mithril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミスリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titanium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイタニアム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stainless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">色褪せぬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">綿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightweight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beautiful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">美しき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逆鱗に触れし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashmere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カシミア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暖かなる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zylon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ザイロン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異国からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spirit cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">霊布</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otherworldly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この世ならざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dawn cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵晒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dusk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵闇をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">griffon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼鳥鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼を折られし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラスチック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transparent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">透き通った</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柔らかい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蜘蛛糸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entangled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絡みつく</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モミ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パルル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明るい土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tropical water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南の島の水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">white sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">強靭なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">willow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cherryblossom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">桜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加工物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">炭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poplar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポプラ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bamboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amethyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメジスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bewitching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖艶なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フェイウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coralwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーラルウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rose quartz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズクオーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lovely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛らしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh cream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生クリーム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">琥珀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マグマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真なる黒曜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lawbreaking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">摂理を断つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elder gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エルダーゴールド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄昏の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orichalcum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オリハルコン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unbreakable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砕けることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abyssal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵を映す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">netherite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネザライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infernal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">煉獄で鍛えられし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無限の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 15.1</t>
@@ -2141,7 +2141,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C7" t="s">
         <v>474</v>
@@ -2189,7 +2189,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C9" t="s">
         <v>476</v>
@@ -2211,7 +2211,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C10" t="s">
         <v>477</v>
@@ -2311,7 +2311,7 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C14" t="s">
         <v>481</v>
@@ -2749,7 +2749,7 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C31" t="s">
         <v>498</v>
@@ -2797,7 +2797,7 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C33" t="s">
         <v>500</v>
@@ -2819,7 +2819,7 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C34" t="s">
         <v>501</v>
@@ -2841,7 +2841,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C35" t="s">
         <v>502</v>
@@ -2863,7 +2863,7 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C36" t="s">
         <v>503</v>
@@ -2885,7 +2885,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C37" t="s">
         <v>504</v>
@@ -2907,7 +2907,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C38" t="s">
         <v>505</v>
@@ -2929,7 +2929,7 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C39" t="s">
         <v>506</v>
@@ -2951,7 +2951,7 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C40" t="s">
         <v>507</v>
@@ -2973,7 +2973,7 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C41" t="s">
         <v>508</v>
@@ -3047,7 +3047,7 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C44" t="s">
         <v>511</v>
@@ -3121,7 +3121,7 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C47" t="s">
         <v>514</v>
@@ -3143,7 +3143,7 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C48" t="s">
         <v>515</v>
@@ -3165,7 +3165,7 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C49" t="s">
         <v>516</v>
@@ -3187,7 +3187,7 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C50" t="s">
         <v>517</v>
@@ -3209,7 +3209,7 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C51" t="s">
         <v>518</v>
@@ -3231,7 +3231,7 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C52" t="s">
         <v>519</v>
@@ -3253,7 +3253,7 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C53" t="s">
         <v>520</v>
@@ -3275,7 +3275,7 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C54" t="s">
         <v>521</v>
@@ -3297,7 +3297,7 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C55" t="s">
         <v>522</v>
@@ -3319,7 +3319,7 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C56" t="s">
         <v>523</v>
@@ -3341,7 +3341,7 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C57" t="s">
         <v>524</v>
@@ -3389,7 +3389,7 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C59" t="s">
         <v>526</v>
@@ -3411,7 +3411,7 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C60" t="s">
         <v>527</v>
@@ -3433,7 +3433,7 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C61" t="s">
         <v>528</v>
@@ -3455,7 +3455,7 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C62" t="s">
         <v>529</v>
@@ -3477,7 +3477,7 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C63" t="s">
         <v>530</v>
@@ -3499,7 +3499,7 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C64" t="s">
         <v>531</v>
@@ -3547,7 +3547,7 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s">
         <v>533</v>
@@ -3569,7 +3569,7 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C67" t="s">
         <v>534</v>
@@ -3591,7 +3591,7 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C68" t="s">
         <v>535</v>
@@ -3613,7 +3613,7 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C69" t="s">
         <v>536</v>
@@ -3635,7 +3635,7 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C70" t="s">
         <v>537</v>
@@ -3943,7 +3943,7 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C82" t="s">
         <v>549</v>
@@ -4017,7 +4017,7 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C85" t="s">
         <v>552</v>
@@ -4039,7 +4039,7 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C86" t="s">
         <v>553</v>
@@ -4061,7 +4061,7 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C87" t="s">
         <v>554</v>
@@ -4083,7 +4083,7 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C88" t="s">
         <v>555</v>
@@ -4105,7 +4105,7 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C89" t="s">
         <v>556</v>
@@ -4127,7 +4127,7 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C90" t="s">
         <v>557</v>
@@ -4149,7 +4149,7 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C91" t="s">
         <v>558</v>
@@ -4171,7 +4171,7 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C92" t="s">
         <v>559</v>
@@ -4193,7 +4193,7 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C93" t="s">
         <v>560</v>
@@ -4241,7 +4241,7 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C95" t="s">
         <v>562</v>
@@ -4263,7 +4263,7 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C96" t="s">
         <v>563</v>
@@ -4285,7 +4285,7 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C97" t="s">
         <v>564</v>
@@ -4307,7 +4307,7 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C98" t="s">
         <v>565</v>
@@ -4329,7 +4329,7 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C99" t="s">
         <v>566</v>
@@ -4351,7 +4351,7 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C100" t="s">
         <v>567</v>
@@ -4373,7 +4373,7 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C101" t="s">
         <v>568</v>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="644">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>
@@ -1389,6 +1389,21 @@
   </si>
   <si>
     <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふわふわの</t>
   </si>
   <si>
     <t xml:space="preserve">EA 23.260</t>
@@ -2037,10 +2052,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -2049,7 +2064,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -2063,10 +2078,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -2075,7 +2090,7 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -2089,10 +2104,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C5" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -2101,7 +2116,7 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -2115,10 +2130,10 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C6" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -2127,7 +2142,7 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="G6" t="s">
         <v>27</v>
@@ -2141,10 +2156,10 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C7" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D7" t="s">
         <v>30</v>
@@ -2153,7 +2168,7 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -2163,10 +2178,10 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C8" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -2175,7 +2190,7 @@
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="G8" t="s">
         <v>35</v>
@@ -2189,10 +2204,10 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C9" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
@@ -2201,7 +2216,7 @@
         <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -2211,10 +2226,10 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C10" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
@@ -2223,7 +2238,7 @@
         <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
@@ -2233,10 +2248,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C11" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D11" t="s">
         <v>44</v>
@@ -2245,7 +2260,7 @@
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="G11" t="s">
         <v>46</v>
@@ -2259,10 +2274,10 @@
         <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C12" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D12" t="s">
         <v>49</v>
@@ -2271,7 +2286,7 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="G12" t="s">
         <v>51</v>
@@ -2285,10 +2300,10 @@
         <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C13" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -2297,7 +2312,7 @@
         <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="G13" t="s">
         <v>56</v>
@@ -2311,10 +2326,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C14" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -2323,7 +2338,7 @@
         <v>60</v>
       </c>
       <c r="F14" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G14"/>
       <c r="H14"/>
@@ -2333,10 +2348,10 @@
         <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C15" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -2345,7 +2360,7 @@
         <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="G15" t="s">
         <v>64</v>
@@ -2359,10 +2374,10 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C16" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D16" t="s">
         <v>67</v>
@@ -2371,7 +2386,7 @@
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="G16" t="s">
         <v>69</v>
@@ -2385,10 +2400,10 @@
         <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C17" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="D17" t="s">
         <v>72</v>
@@ -2397,7 +2412,7 @@
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="G17" t="s">
         <v>74</v>
@@ -2411,10 +2426,10 @@
         <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C18" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -2423,7 +2438,7 @@
         <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="G18" t="s">
         <v>79</v>
@@ -2437,10 +2452,10 @@
         <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C19" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D19" t="s">
         <v>82</v>
@@ -2449,7 +2464,7 @@
         <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="G19" t="s">
         <v>84</v>
@@ -2463,10 +2478,10 @@
         <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C20" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="D20" t="s">
         <v>87</v>
@@ -2475,7 +2490,7 @@
         <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="G20" t="s">
         <v>89</v>
@@ -2489,10 +2504,10 @@
         <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C21" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="D21" t="s">
         <v>92</v>
@@ -2501,7 +2516,7 @@
         <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G21" t="s">
         <v>94</v>
@@ -2515,10 +2530,10 @@
         <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C22" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D22" t="s">
         <v>97</v>
@@ -2527,7 +2542,7 @@
         <v>98</v>
       </c>
       <c r="F22" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -2541,10 +2556,10 @@
         <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C23" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D23" t="s">
         <v>102</v>
@@ -2553,7 +2568,7 @@
         <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="G23" t="s">
         <v>104</v>
@@ -2567,10 +2582,10 @@
         <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C24" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="D24" t="s">
         <v>107</v>
@@ -2579,7 +2594,7 @@
         <v>108</v>
       </c>
       <c r="F24" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="G24" t="s">
         <v>109</v>
@@ -2593,10 +2608,10 @@
         <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C25" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D25" t="s">
         <v>112</v>
@@ -2605,7 +2620,7 @@
         <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="G25" t="s">
         <v>114</v>
@@ -2619,10 +2634,10 @@
         <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C26" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D26" t="s">
         <v>117</v>
@@ -2631,7 +2646,7 @@
         <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="G26" t="s">
         <v>119</v>
@@ -2645,10 +2660,10 @@
         <v>121</v>
       </c>
       <c r="B27" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C27" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D27" t="s">
         <v>122</v>
@@ -2657,7 +2672,7 @@
         <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="G27" t="s">
         <v>124</v>
@@ -2671,10 +2686,10 @@
         <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C28" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D28" t="s">
         <v>127</v>
@@ -2683,7 +2698,7 @@
         <v>128</v>
       </c>
       <c r="F28" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="G28" t="s">
         <v>129</v>
@@ -2697,10 +2712,10 @@
         <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C29" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D29" t="s">
         <v>132</v>
@@ -2709,7 +2724,7 @@
         <v>133</v>
       </c>
       <c r="F29" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="G29" t="s">
         <v>134</v>
@@ -2723,10 +2738,10 @@
         <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C30" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
@@ -2735,7 +2750,7 @@
         <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="G30" t="s">
         <v>139</v>
@@ -2749,10 +2764,10 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C31" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D31" t="s">
         <v>142</v>
@@ -2761,7 +2776,7 @@
         <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
@@ -2771,10 +2786,10 @@
         <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C32" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -2783,7 +2798,7 @@
         <v>146</v>
       </c>
       <c r="F32" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="G32" t="s">
         <v>147</v>
@@ -2797,10 +2812,10 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C33" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="D33" t="s">
         <v>150</v>
@@ -2809,7 +2824,7 @@
         <v>151</v>
       </c>
       <c r="F33" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -2819,10 +2834,10 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C34" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D34" t="s">
         <v>153</v>
@@ -2831,7 +2846,7 @@
         <v>154</v>
       </c>
       <c r="F34" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
@@ -2841,10 +2856,10 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -2853,7 +2868,7 @@
         <v>157</v>
       </c>
       <c r="F35" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
@@ -2863,10 +2878,10 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C36" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="D36" t="s">
         <v>159</v>
@@ -2875,7 +2890,7 @@
         <v>160</v>
       </c>
       <c r="F36" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
@@ -2885,10 +2900,10 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C37" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D37" t="s">
         <v>162</v>
@@ -2897,7 +2912,7 @@
         <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
@@ -2907,10 +2922,10 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C38" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D38" t="s">
         <v>165</v>
@@ -2919,7 +2934,7 @@
         <v>166</v>
       </c>
       <c r="F38" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
@@ -2929,10 +2944,10 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C39" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D39" t="s">
         <v>168</v>
@@ -2941,7 +2956,7 @@
         <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
@@ -2951,10 +2966,10 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C40" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D40" t="s">
         <v>171</v>
@@ -2963,7 +2978,7 @@
         <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -2973,10 +2988,10 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C41" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D41" t="s">
         <v>174</v>
@@ -2985,7 +3000,7 @@
         <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
@@ -2995,10 +3010,10 @@
         <v>176</v>
       </c>
       <c r="B42" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C42" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D42" t="s">
         <v>177</v>
@@ -3007,7 +3022,7 @@
         <v>178</v>
       </c>
       <c r="F42" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="G42" t="s">
         <v>179</v>
@@ -3021,10 +3036,10 @@
         <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C43" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D43" t="s">
         <v>182</v>
@@ -3033,7 +3048,7 @@
         <v>183</v>
       </c>
       <c r="F43" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="G43" t="s">
         <v>184</v>
@@ -3047,10 +3062,10 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C44" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D44" t="s">
         <v>187</v>
@@ -3059,7 +3074,7 @@
         <v>188</v>
       </c>
       <c r="F44" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
@@ -3069,10 +3084,10 @@
         <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C45" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="D45" t="s">
         <v>190</v>
@@ -3081,7 +3096,7 @@
         <v>191</v>
       </c>
       <c r="F45" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="G45" t="s">
         <v>192</v>
@@ -3095,10 +3110,10 @@
         <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C46" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D46" t="s">
         <v>195</v>
@@ -3107,7 +3122,7 @@
         <v>196</v>
       </c>
       <c r="F46" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G46" t="s">
         <v>197</v>
@@ -3121,10 +3136,10 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C47" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="D47" t="s">
         <v>200</v>
@@ -3133,7 +3148,7 @@
         <v>201</v>
       </c>
       <c r="F47" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
@@ -3143,10 +3158,10 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C48" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D48" t="s">
         <v>203</v>
@@ -3155,7 +3170,7 @@
         <v>204</v>
       </c>
       <c r="F48" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -3165,10 +3180,10 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C49" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="D49" t="s">
         <v>206</v>
@@ -3177,7 +3192,7 @@
         <v>207</v>
       </c>
       <c r="F49" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
@@ -3187,10 +3202,10 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C50" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="D50" t="s">
         <v>209</v>
@@ -3199,7 +3214,7 @@
         <v>210</v>
       </c>
       <c r="F50" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
@@ -3209,10 +3224,10 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C51" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="D51" t="s">
         <v>212</v>
@@ -3221,7 +3236,7 @@
         <v>213</v>
       </c>
       <c r="F51" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -3231,10 +3246,10 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C52" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D52" t="s">
         <v>215</v>
@@ -3243,7 +3258,7 @@
         <v>216</v>
       </c>
       <c r="F52" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -3253,10 +3268,10 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C53" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="D53" t="s">
         <v>218</v>
@@ -3265,7 +3280,7 @@
         <v>219</v>
       </c>
       <c r="F53" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -3275,10 +3290,10 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C54" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="D54" t="s">
         <v>221</v>
@@ -3287,7 +3302,7 @@
         <v>222</v>
       </c>
       <c r="F54" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -3297,10 +3312,10 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C55" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="D55" t="s">
         <v>224</v>
@@ -3309,7 +3324,7 @@
         <v>225</v>
       </c>
       <c r="F55" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -3319,10 +3334,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C56" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3331,7 +3346,7 @@
         <v>228</v>
       </c>
       <c r="F56" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -3341,10 +3356,10 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C57" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3353,7 +3368,7 @@
         <v>231</v>
       </c>
       <c r="F57" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -3363,10 +3378,10 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C58" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3375,7 +3390,7 @@
         <v>234</v>
       </c>
       <c r="F58" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="G58" t="s">
         <v>235</v>
@@ -3389,10 +3404,10 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C59" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D59" t="s">
         <v>238</v>
@@ -3401,7 +3416,7 @@
         <v>239</v>
       </c>
       <c r="F59" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -3411,10 +3426,10 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C60" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
@@ -3423,7 +3438,7 @@
         <v>242</v>
       </c>
       <c r="F60" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -3433,10 +3448,10 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C61" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
@@ -3445,7 +3460,7 @@
         <v>245</v>
       </c>
       <c r="F61" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -3455,10 +3470,10 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C62" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="D62" t="s">
         <v>247</v>
@@ -3467,7 +3482,7 @@
         <v>248</v>
       </c>
       <c r="F62" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -3477,10 +3492,10 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C63" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="D63" t="s">
         <v>250</v>
@@ -3489,7 +3504,7 @@
         <v>251</v>
       </c>
       <c r="F63" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -3499,10 +3514,10 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C64" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="D64" t="s">
         <v>253</v>
@@ -3511,7 +3526,7 @@
         <v>254</v>
       </c>
       <c r="F64" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -3521,10 +3536,10 @@
         <v>255</v>
       </c>
       <c r="B65" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C65" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="D65" t="s">
         <v>256</v>
@@ -3533,7 +3548,7 @@
         <v>257</v>
       </c>
       <c r="F65" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="G65" t="s">
         <v>258</v>
@@ -3547,10 +3562,10 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C66" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="D66" t="s">
         <v>261</v>
@@ -3559,7 +3574,7 @@
         <v>262</v>
       </c>
       <c r="F66" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -3569,10 +3584,10 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C67" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D67" t="s">
         <v>264</v>
@@ -3581,7 +3596,7 @@
         <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -3591,10 +3606,10 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C68" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D68" t="s">
         <v>267</v>
@@ -3603,7 +3618,7 @@
         <v>268</v>
       </c>
       <c r="F68" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -3613,10 +3628,10 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C69" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="D69" t="s">
         <v>270</v>
@@ -3625,7 +3640,7 @@
         <v>271</v>
       </c>
       <c r="F69" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -3635,10 +3650,10 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C70" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="D70" t="s">
         <v>273</v>
@@ -3647,7 +3662,7 @@
         <v>274</v>
       </c>
       <c r="F70" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -3657,10 +3672,10 @@
         <v>275</v>
       </c>
       <c r="B71" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C71" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="D71" t="s">
         <v>276</v>
@@ -3669,7 +3684,7 @@
         <v>277</v>
       </c>
       <c r="F71" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="G71" t="s">
         <v>278</v>
@@ -3683,10 +3698,10 @@
         <v>280</v>
       </c>
       <c r="B72" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C72" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D72" t="s">
         <v>281</v>
@@ -3695,7 +3710,7 @@
         <v>282</v>
       </c>
       <c r="F72" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="G72" t="s">
         <v>283</v>
@@ -3709,10 +3724,10 @@
         <v>285</v>
       </c>
       <c r="B73" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C73" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D73" t="s">
         <v>286</v>
@@ -3721,7 +3736,7 @@
         <v>287</v>
       </c>
       <c r="F73" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="G73" t="s">
         <v>288</v>
@@ -3735,10 +3750,10 @@
         <v>290</v>
       </c>
       <c r="B74" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C74" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D74" t="s">
         <v>291</v>
@@ -3747,7 +3762,7 @@
         <v>292</v>
       </c>
       <c r="F74" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="G74" t="s">
         <v>293</v>
@@ -3761,10 +3776,10 @@
         <v>295</v>
       </c>
       <c r="B75" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C75" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D75" t="s">
         <v>296</v>
@@ -3773,7 +3788,7 @@
         <v>297</v>
       </c>
       <c r="F75" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="G75" t="s">
         <v>298</v>
@@ -3787,10 +3802,10 @@
         <v>300</v>
       </c>
       <c r="B76" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C76" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D76" t="s">
         <v>301</v>
@@ -3799,7 +3814,7 @@
         <v>302</v>
       </c>
       <c r="F76" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="G76" t="s">
         <v>303</v>
@@ -3813,10 +3828,10 @@
         <v>305</v>
       </c>
       <c r="B77" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C77" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="D77" t="s">
         <v>306</v>
@@ -3825,7 +3840,7 @@
         <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="G77" t="s">
         <v>308</v>
@@ -3839,10 +3854,10 @@
         <v>310</v>
       </c>
       <c r="B78" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C78" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D78" t="s">
         <v>311</v>
@@ -3851,7 +3866,7 @@
         <v>312</v>
       </c>
       <c r="F78" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G78" t="s">
         <v>313</v>
@@ -3865,10 +3880,10 @@
         <v>315</v>
       </c>
       <c r="B79" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C79" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D79" t="s">
         <v>316</v>
@@ -3877,7 +3892,7 @@
         <v>317</v>
       </c>
       <c r="F79" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="G79" t="s">
         <v>318</v>
@@ -3891,10 +3906,10 @@
         <v>320</v>
       </c>
       <c r="B80" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C80" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="D80" t="s">
         <v>321</v>
@@ -3903,7 +3918,7 @@
         <v>322</v>
       </c>
       <c r="F80" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="G80" t="s">
         <v>323</v>
@@ -3917,10 +3932,10 @@
         <v>325</v>
       </c>
       <c r="B81" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C81" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D81" t="s">
         <v>326</v>
@@ -3929,7 +3944,7 @@
         <v>327</v>
       </c>
       <c r="F81" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G81" t="s">
         <v>328</v>
@@ -3943,10 +3958,10 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C82" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D82" t="s">
         <v>331</v>
@@ -3955,7 +3970,7 @@
         <v>332</v>
       </c>
       <c r="F82" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
@@ -3965,10 +3980,10 @@
         <v>333</v>
       </c>
       <c r="B83" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C83" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D83" t="s">
         <v>334</v>
@@ -3977,7 +3992,7 @@
         <v>335</v>
       </c>
       <c r="F83" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="G83" t="s">
         <v>336</v>
@@ -3991,10 +4006,10 @@
         <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C84" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D84" t="s">
         <v>339</v>
@@ -4003,7 +4018,7 @@
         <v>340</v>
       </c>
       <c r="F84" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="G84" t="s">
         <v>341</v>
@@ -4017,10 +4032,10 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C85" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="D85" t="s">
         <v>344</v>
@@ -4029,7 +4044,7 @@
         <v>345</v>
       </c>
       <c r="F85" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
@@ -4039,10 +4054,10 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C86" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D86" t="s">
         <v>347</v>
@@ -4051,7 +4066,7 @@
         <v>348</v>
       </c>
       <c r="F86" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
@@ -4061,10 +4076,10 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C87" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D87" t="s">
         <v>350</v>
@@ -4073,7 +4088,7 @@
         <v>351</v>
       </c>
       <c r="F87" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
@@ -4083,10 +4098,10 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C88" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D88" t="s">
         <v>353</v>
@@ -4095,7 +4110,7 @@
         <v>354</v>
       </c>
       <c r="F88" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
@@ -4105,10 +4120,10 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C89" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="D89" t="s">
         <v>356</v>
@@ -4117,7 +4132,7 @@
         <v>357</v>
       </c>
       <c r="F89" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
@@ -4127,10 +4142,10 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C90" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="D90" t="s">
         <v>359</v>
@@ -4139,7 +4154,7 @@
         <v>360</v>
       </c>
       <c r="F90" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
@@ -4149,10 +4164,10 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C91" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D91" t="s">
         <v>362</v>
@@ -4161,7 +4176,7 @@
         <v>363</v>
       </c>
       <c r="F91" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
@@ -4171,10 +4186,10 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C92" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D92" t="s">
         <v>365</v>
@@ -4183,7 +4198,7 @@
         <v>366</v>
       </c>
       <c r="F92" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>
@@ -4193,10 +4208,10 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C93" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="D93" t="s">
         <v>368</v>
@@ -4205,7 +4220,7 @@
         <v>369</v>
       </c>
       <c r="F93" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G93"/>
       <c r="H93"/>
@@ -4215,10 +4230,10 @@
         <v>370</v>
       </c>
       <c r="B94" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C94" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="D94" t="s">
         <v>371</v>
@@ -4227,7 +4242,7 @@
         <v>372</v>
       </c>
       <c r="F94" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="G94" t="s">
         <v>373</v>
@@ -4241,10 +4256,10 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C95" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D95" t="s">
         <v>376</v>
@@ -4253,7 +4268,7 @@
         <v>377</v>
       </c>
       <c r="F95" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
@@ -4263,10 +4278,10 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C96" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="D96" t="s">
         <v>379</v>
@@ -4275,7 +4290,7 @@
         <v>380</v>
       </c>
       <c r="F96" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
@@ -4285,10 +4300,10 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C97" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D97" t="s">
         <v>382</v>
@@ -4297,7 +4312,7 @@
         <v>383</v>
       </c>
       <c r="F97" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
@@ -4307,10 +4322,10 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D98" t="s">
         <v>385</v>
@@ -4319,7 +4334,7 @@
         <v>386</v>
       </c>
       <c r="F98" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -4329,10 +4344,10 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C99" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="D99" t="s">
         <v>388</v>
@@ -4341,7 +4356,7 @@
         <v>389</v>
       </c>
       <c r="F99" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
@@ -4351,10 +4366,10 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C100" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="D100" t="s">
         <v>391</v>
@@ -4363,7 +4378,7 @@
         <v>392</v>
       </c>
       <c r="F100" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
@@ -4373,10 +4388,10 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C101" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D101" t="s">
         <v>394</v>
@@ -4385,7 +4400,7 @@
         <v>395</v>
       </c>
       <c r="F101" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
@@ -4395,10 +4410,10 @@
         <v>396</v>
       </c>
       <c r="B102" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C102" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="D102" t="s">
         <v>397</v>
@@ -4407,7 +4422,7 @@
         <v>398</v>
       </c>
       <c r="F102" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="G102" t="s">
         <v>399</v>
@@ -4421,10 +4436,10 @@
         <v>401</v>
       </c>
       <c r="B103" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C103" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="D103" t="s">
         <v>402</v>
@@ -4440,10 +4455,10 @@
         <v>404</v>
       </c>
       <c r="B104" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C104" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D104" t="s">
         <v>405</v>
@@ -4459,10 +4474,10 @@
         <v>407</v>
       </c>
       <c r="B105" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C105" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="D105" t="s">
         <v>408</v>
@@ -4471,7 +4486,7 @@
         <v>409</v>
       </c>
       <c r="F105" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="G105" t="s">
         <v>410</v>
@@ -4485,10 +4500,10 @@
         <v>412</v>
       </c>
       <c r="B106" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C106" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D106" t="s">
         <v>413</v>
@@ -4504,10 +4519,10 @@
         <v>415</v>
       </c>
       <c r="B107" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C107" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="D107" t="s">
         <v>416</v>
@@ -4523,10 +4538,10 @@
         <v>418</v>
       </c>
       <c r="B108" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C108" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="D108" t="s">
         <v>419</v>
@@ -4542,10 +4557,10 @@
         <v>421</v>
       </c>
       <c r="B109" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C109" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="D109" t="s">
         <v>422</v>
@@ -4561,10 +4576,10 @@
         <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C110" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="D110" t="s">
         <v>425</v>
@@ -4573,7 +4588,7 @@
         <v>426</v>
       </c>
       <c r="F110" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="G110" t="s">
         <v>427</v>
@@ -4587,10 +4602,10 @@
         <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C111" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="D111" t="s">
         <v>430</v>
@@ -4599,7 +4614,7 @@
         <v>431</v>
       </c>
       <c r="F111" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="G111" t="s">
         <v>318</v>
@@ -4613,10 +4628,10 @@
         <v>433</v>
       </c>
       <c r="B112" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C112" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D112" t="s">
         <v>434</v>
@@ -4625,7 +4640,7 @@
         <v>435</v>
       </c>
       <c r="F112" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="G112" t="s">
         <v>436</v>
@@ -4639,10 +4654,10 @@
         <v>438</v>
       </c>
       <c r="B113" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C113" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="D113" t="s">
         <v>439</v>
@@ -4651,7 +4666,7 @@
         <v>440</v>
       </c>
       <c r="F113" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="G113" t="s">
         <v>441</v>
@@ -4665,10 +4680,10 @@
         <v>443</v>
       </c>
       <c r="B114" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C114" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="D114" t="s">
         <v>444</v>
@@ -4677,7 +4692,7 @@
         <v>445</v>
       </c>
       <c r="F114" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="G114" t="s">
         <v>446</v>
@@ -4691,10 +4706,10 @@
         <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C115" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="D115" t="s">
         <v>449</v>
@@ -4703,7 +4718,7 @@
         <v>450</v>
       </c>
       <c r="F115" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="G115" t="s">
         <v>451</v>
@@ -4717,10 +4732,10 @@
         <v>453</v>
       </c>
       <c r="B116" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C116" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="D116" t="s">
         <v>454</v>
@@ -4729,13 +4744,33 @@
         <v>455</v>
       </c>
       <c r="F116" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="G116" t="s">
         <v>456</v>
       </c>
       <c r="H116" t="s">
         <v>457</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>458</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" t="s">
+        <v>459</v>
+      </c>
+      <c r="E117" t="s">
+        <v>460</v>
+      </c>
+      <c r="G117" t="s">
+        <v>461</v>
+      </c>
+      <c r="H117" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="647">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,1378 +44,1378 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダークマター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest,wooden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森から生まれし,木の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄塊と呼ばれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラナイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rigid,stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩をも砕く,石の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">練習用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深い草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子供のおもちゃの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゼリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trembling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プルプルする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生もの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカシア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄金に輝く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreadbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を砕く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雷を帯し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気高き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミカ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ephemeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">儚き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unveiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真実を暴く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイヤモンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">everlasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変わることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubynus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルビナス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤く染まった</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由緒ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珊瑚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quartz sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珪砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glittering,glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さざめく,ガラスの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminescent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異光を放つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">革</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全てを包む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draconic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜を統べし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真珠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を照らす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エメラルド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇跡を呼ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コバルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adamantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アダマンタイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthshaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大地を揺るがす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapphire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サファイア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トパーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquamarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アクアマリン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オパール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翡翠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニキス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapis lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラピス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターコイズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meteorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メテオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platinum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brilliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不死なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふざけた</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エーテル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永遠なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライムストーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大理石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バサルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒曜石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">godbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神殺しの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phyllite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot spring water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pale soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い色の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mahogany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マホガニー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rosewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farmwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">農作業用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミスリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ancient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイタニアム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色褪せぬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">綿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beautiful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美しき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逆鱗に触れし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cashmere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カシミア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暖かなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザイロン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異国からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spirit cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">霊布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherworldly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この世ならざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawn cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵晒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵闇をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">griffon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼鳥鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼を折られし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プラスチック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透き通った</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柔らかい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spider silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜘蛛糸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entangled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絡みつく</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モミ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パルル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明るい土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tropical water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南の島の水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強靭なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cherryblossom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">桜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加工物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poplar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポプラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amethyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アメジスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bewitching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖艶なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フェイウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coralwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーラルウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズクオーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛らしい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh cream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生クリーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">琥珀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マグマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真なる黒曜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lawbreaking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">摂理を断つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elder gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エルダーゴールド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄昏の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orichalcum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オリハルコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unbreakable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砕けることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abyssal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵を映す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netherite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネザライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infernal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉獄で鍛えられし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふわふわの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dark matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダークマター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オーク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest,wooden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森から生まれし,木の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄塊と呼ばれる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラナイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rigid,stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩をも砕く,石の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">練習用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深い草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子供のおもちゃの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゼリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trembling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プルプルする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生もの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アカシア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄金に輝く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dreadbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を砕く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雷を帯し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">気高き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミカ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ephemeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">儚き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chromite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unveiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真実を暴く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイヤモンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everlasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変わることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubynus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルビナス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤く染まった</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">historic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">由緒ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珊瑚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quartz sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珪砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glittering,glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">さざめく,ガラスの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異光を放つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">革</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mysterious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全てを包む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draconic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜を統べし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真珠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を照らす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エメラルド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇跡を呼ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cobalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コバルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adamantite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アダマンタイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">earthshaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大地を揺るがす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapphire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サファイア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トパーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquamarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アクアマリン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オパール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翡翠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onyx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オニキス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapis lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラピス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターコイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meteorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メテオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platinum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brilliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不死なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">birch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふざけた</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エーテル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永遠なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ライムストーン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大理石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バサルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黒曜石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">godbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神殺しの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phyllite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot spring water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pale soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い色の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahogany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マホガニー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rosewood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farmwork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">農作業用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cedar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mithril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミスリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titanium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイタニアム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stainless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">色褪せぬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">綿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightweight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beautiful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">美しき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逆鱗に触れし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashmere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カシミア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暖かなる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zylon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ザイロン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異国からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spirit cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">霊布</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otherworldly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この世ならざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dawn cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵晒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dusk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵闇をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">griffon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼鳥鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼を折られし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラスチック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transparent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">透き通った</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柔らかい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蜘蛛糸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entangled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絡みつく</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モミ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パルル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明るい土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tropical water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南の島の水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">white sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">強靭なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">willow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cherryblossom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">桜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加工物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">炭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poplar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポプラ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bamboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amethyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメジスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bewitching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖艶なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フェイウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coralwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーラルウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rose quartz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズクオーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lovely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛らしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh cream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生クリーム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">琥珀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マグマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真なる黒曜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lawbreaking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">摂理を断つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elder gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エルダーゴールド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄昏の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orichalcum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オリハルコン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unbreakable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砕けることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abyssal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵を映す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">netherite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネザライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infernal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">煉獄で鍛えられし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無限の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雲</t>
-  </si>
-  <si>
-    <t xml:space="preserve">puffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふわふわの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 15.1</t>
@@ -2165,7 +2165,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C7" t="s">
         <v>480</v>
@@ -2213,7 +2213,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C9" t="s">
         <v>482</v>
@@ -2235,7 +2235,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C10" t="s">
         <v>483</v>
@@ -2335,7 +2335,7 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C14" t="s">
         <v>487</v>
@@ -2773,7 +2773,7 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C31" t="s">
         <v>504</v>
@@ -2821,7 +2821,7 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C33" t="s">
         <v>506</v>
@@ -2843,7 +2843,7 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C34" t="s">
         <v>507</v>
@@ -2865,7 +2865,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C35" t="s">
         <v>508</v>
@@ -2887,7 +2887,7 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C36" t="s">
         <v>509</v>
@@ -2909,7 +2909,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C37" t="s">
         <v>510</v>
@@ -2931,7 +2931,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C38" t="s">
         <v>511</v>
@@ -2953,7 +2953,7 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C39" t="s">
         <v>512</v>
@@ -2975,7 +2975,7 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C40" t="s">
         <v>513</v>
@@ -2997,7 +2997,7 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C41" t="s">
         <v>514</v>
@@ -3071,7 +3071,7 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C44" t="s">
         <v>517</v>
@@ -3145,7 +3145,7 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C47" t="s">
         <v>520</v>
@@ -3167,7 +3167,7 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C48" t="s">
         <v>521</v>
@@ -3189,7 +3189,7 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C49" t="s">
         <v>522</v>
@@ -3211,7 +3211,7 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C50" t="s">
         <v>523</v>
@@ -3233,7 +3233,7 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C51" t="s">
         <v>524</v>
@@ -3255,7 +3255,7 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C52" t="s">
         <v>525</v>
@@ -3277,7 +3277,7 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C53" t="s">
         <v>526</v>
@@ -3299,7 +3299,7 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C54" t="s">
         <v>527</v>
@@ -3321,7 +3321,7 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C55" t="s">
         <v>528</v>
@@ -3343,7 +3343,7 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C56" t="s">
         <v>529</v>
@@ -3365,7 +3365,7 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C57" t="s">
         <v>530</v>
@@ -3413,7 +3413,7 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C59" t="s">
         <v>532</v>
@@ -3435,7 +3435,7 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C60" t="s">
         <v>533</v>
@@ -3457,7 +3457,7 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C61" t="s">
         <v>534</v>
@@ -3479,7 +3479,7 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C62" t="s">
         <v>535</v>
@@ -3501,7 +3501,7 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C63" t="s">
         <v>536</v>
@@ -3523,7 +3523,7 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C64" t="s">
         <v>537</v>
@@ -3571,7 +3571,7 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C66" t="s">
         <v>539</v>
@@ -3593,7 +3593,7 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C67" t="s">
         <v>540</v>
@@ -3615,7 +3615,7 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C68" t="s">
         <v>541</v>
@@ -3637,7 +3637,7 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C69" t="s">
         <v>542</v>
@@ -3659,7 +3659,7 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C70" t="s">
         <v>543</v>
@@ -3967,7 +3967,7 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C82" t="s">
         <v>555</v>
@@ -4041,7 +4041,7 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C85" t="s">
         <v>558</v>
@@ -4063,7 +4063,7 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C86" t="s">
         <v>559</v>
@@ -4085,7 +4085,7 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C87" t="s">
         <v>560</v>
@@ -4107,7 +4107,7 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C88" t="s">
         <v>561</v>
@@ -4129,7 +4129,7 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C89" t="s">
         <v>562</v>
@@ -4151,7 +4151,7 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C90" t="s">
         <v>563</v>
@@ -4173,7 +4173,7 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C91" t="s">
         <v>564</v>
@@ -4195,7 +4195,7 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C92" t="s">
         <v>565</v>
@@ -4217,7 +4217,7 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C93" t="s">
         <v>566</v>
@@ -4265,7 +4265,7 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C95" t="s">
         <v>568</v>
@@ -4287,7 +4287,7 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C96" t="s">
         <v>569</v>
@@ -4309,7 +4309,7 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C97" t="s">
         <v>570</v>
@@ -4331,7 +4331,7 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
         <v>571</v>
@@ -4353,7 +4353,7 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C99" t="s">
         <v>572</v>
@@ -4375,7 +4375,7 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C100" t="s">
         <v>573</v>
@@ -4397,7 +4397,7 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C101" t="s">
         <v>574</v>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>
